--- a/cleansheet/tests/fixtures/expected/messy_contacts_cleaned.xlsx
+++ b/cleansheet/tests/fixtures/expected/messy_contacts_cleaned.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>555-1234</t>
+          <t>5551234</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>555-5678</t>
+          <t>5555678</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>555-9012</t>
+          <t>5559012</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>555-3456</t>
+          <t>5553456</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>555-7890</t>
+          <t>5557890</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>555-1111</t>
+          <t>5551111</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>555-2222</t>
+          <t>5552222</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>555-3333</t>
+          <t>5553333</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>555-4444</t>
+          <t>5554444</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>555-5555</t>
+          <t>5555555</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>555-6666</t>
+          <t>5556666</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>555-7777</t>
+          <t>5557777</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
